--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/magallanes.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -758,7 +758,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1057402-6584-CM26</t>
+          <t>1057402-6581-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1057402-6581-CM26</t>
+          <t>1057402-6577-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -880,7 +880,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057402-6577-CM26</t>
+          <t>1057402-6571-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057402-6571-CM26</t>
+          <t>1057402-6584-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1057402-7271-CM26</t>
+          <t>1057402-7006-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3714.9</v>
+        <v>7252.55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1057402-7273-CM26</t>
+          <t>1057402-7196-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5691.39</v>
+        <v>6414.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1057402-7247-CM26</t>
+          <t>1057402-7241-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5836.56</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="21">
@@ -1734,7 +1734,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1057402-7241-CM26</t>
+          <t>1057402-7247-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3714.9</v>
+        <v>5836.56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1057402-7196-CM26</t>
+          <t>1057402-7271-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6414.13</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057402-7006-CM26</t>
+          <t>1057402-7273-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7252.55</v>
+        <v>5691.39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057402-7447-CM26</t>
+          <t>1057402-7511-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6323.65</v>
+        <v>4281.44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057402-7507-CM26</t>
+          <t>1057402-7509-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3722.02</v>
+        <v>4197.93</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057402-7509-CM26</t>
+          <t>1057402-7447-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4197.93</v>
+        <v>6323.65</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057402-7511-CM26</t>
+          <t>1057402-7507-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4281.44</v>
+        <v>3722.02</v>
       </c>
     </row>
     <row r="29">
@@ -2222,7 +2222,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1057402-8189-CM26</t>
+          <t>1057402-7871-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7146.38</v>
+        <v>6470.64</v>
       </c>
     </row>
     <row r="31">
@@ -2344,7 +2344,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1057402-7871-CM26</t>
+          <t>1057402-8189-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>6470.64</v>
+        <v>7146.38</v>
       </c>
     </row>
     <row r="33">
@@ -2588,7 +2588,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057402-8322-CM26</t>
+          <t>1057402-8336-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2800.66</v>
+        <v>4552.93</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1057402-8334-CM26</t>
+          <t>1057402-8592-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>5201.68</v>
+        <v>3784.84</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1057402-8336-CM26</t>
+          <t>1057402-8511-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4552.93</v>
+        <v>4188.09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1057402-8508-CM26</t>
+          <t>1057402-8334-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5946.43</v>
+        <v>5201.68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1057402-8511-CM26</t>
+          <t>1057402-8322-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4188.09</v>
+        <v>2800.66</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057402-8592-CM26</t>
+          <t>1057402-8508-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2948,7 +2948,495 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3784.84</v>
+        <v>5946.43</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1057402-9135-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>4463.31</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1057402-8807-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>3710.34</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1057402-8811-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>4105.65</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1057402-8818-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>5892.31</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1057402-8820-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>3710.34</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1057402-9564-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>5336.51</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1057402-10002-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>4873.15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1057402-10037-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>4312.16</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/magallanes.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/magallanes.xlsx
@@ -684,7 +684,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1603,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2400,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2587,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2896,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3327,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3392,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/magallanes.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1057402-6483-CM26</t>
+          <t>1057402-6565-CM26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7110.27</v>
+        <v>3974.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1057402-6695-CM26</t>
+          <t>1057402-6694-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -615,28 +615,32 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4040.37</v>
+        <v>2528.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1057402-6694-CM26</t>
+          <t>1057402-6588-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -676,32 +680,28 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2528.71</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057402-6588-CM26</t>
+          <t>1057402-6483-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -756,13 +756,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3859.73</v>
+        <v>7110.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1057402-6581-CM26</t>
+          <t>1057402-6485-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3859.73</v>
+        <v>8393.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1057402-6577-CM26</t>
+          <t>1057402-6488-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -884,7 +884,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057402-6571-CM26</t>
+          <t>1057402-6510-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1057402-6569-CM26</t>
+          <t>1057402-6514-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4439.84</v>
+        <v>4353.24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057402-6584-CM26</t>
+          <t>1057402-6564-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057402-6565-CM26</t>
+          <t>1057402-6695-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3974.88</v>
+        <v>4040.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1057402-6564-CM26</t>
+          <t>1057402-6566-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3859.73</v>
+        <v>4353.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1057402-6514-CM26</t>
+          <t>1057402-6569-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4353.24</v>
+        <v>4439.84</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1057402-6510-CM26</t>
+          <t>1057402-6571-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1311,7 +1311,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1057402-6488-CM26</t>
+          <t>1057402-6577-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1372,7 +1372,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1057402-6485-CM26</t>
+          <t>1057402-6581-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8393.73</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1057402-6566-CM26</t>
+          <t>1057402-6584-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4353.24</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1057402-7006-CM26</t>
+          <t>1057402-7273-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7252.55</v>
+        <v>5691.39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1057402-7196-CM26</t>
+          <t>1057402-7271-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1595,32 +1595,28 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6414.13</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1057402-7241-CM26</t>
+          <t>1057402-7247-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1675,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3714.9</v>
+        <v>5836.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1057402-7245-CM26</t>
+          <t>1057402-7241-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4273.24</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1057402-7247-CM26</t>
+          <t>1057402-7245-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1797,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5836.56</v>
+        <v>4273.24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1057402-7271-CM26</t>
+          <t>1057402-7006-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1858,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3714.9</v>
+        <v>7252.55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057402-7273-CM26</t>
+          <t>1057402-7196-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1904,28 +1900,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5691.39</v>
+        <v>6414.13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057402-7511-CM26</t>
+          <t>1057402-7447-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4281.44</v>
+        <v>6323.65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057402-7509-CM26</t>
+          <t>1057402-7507-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2041,13 +2041,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4197.93</v>
+        <v>3722.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057402-7447-CM26</t>
+          <t>1057402-7509-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6323.65</v>
+        <v>4197.93</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057402-7507-CM26</t>
+          <t>1057402-7511-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3722.02</v>
+        <v>4281.44</v>
       </c>
     </row>
     <row r="29">
@@ -2230,7 +2230,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1057402-7871-CM26</t>
+          <t>1057402-8011-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>6470.64</v>
+        <v>3744.07</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057402-8011-CM26</t>
+          <t>1057402-7871-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3744.07</v>
+        <v>6470.64</v>
       </c>
     </row>
     <row r="32">
@@ -2604,7 +2604,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057402-8336-CM26</t>
+          <t>1057402-8322-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2644,28 +2644,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4552.93</v>
+        <v>2800.66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1057402-8592-CM26</t>
+          <t>1057402-8334-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2720,13 +2724,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3784.84</v>
+        <v>5201.68</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1057402-8511-CM26</t>
+          <t>1057402-8336-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2781,13 +2785,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4188.09</v>
+        <v>4552.93</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1057402-8334-CM26</t>
+          <t>1057402-8508-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2842,13 +2846,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5201.68</v>
+        <v>5946.43</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1057402-8322-CM26</t>
+          <t>1057402-8511-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2888,32 +2892,28 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2800.66</v>
+        <v>4188.09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057402-8508-CM26</t>
+          <t>1057402-8592-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5946.43</v>
+        <v>3784.84</v>
       </c>
     </row>
     <row r="42">
@@ -3035,7 +3035,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1057402-8807-CM26</t>
+          <t>1057402-8811-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3090,13 +3090,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3710.34</v>
+        <v>4105.65</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057402-8811-CM26</t>
+          <t>1057402-8807-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3151,13 +3151,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4105.65</v>
+        <v>3710.34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1057402-8818-CM26</t>
+          <t>1057402-8820-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3212,13 +3212,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>5892.31</v>
+        <v>3710.34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057402-8820-CM26</t>
+          <t>1057402-8818-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3710.34</v>
+        <v>5892.31</v>
       </c>
     </row>
     <row r="47">
@@ -3344,7 +3344,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1057402-10002-CM26</t>
+          <t>1057402-10037-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3384,32 +3384,28 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4873.15</v>
+        <v>4312.16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1057402-10037-CM26</t>
+          <t>1057402-10002-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3449,22 +3445,217 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>4312.16</v>
+        <v>4873.15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1057402-10852-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>5558.97</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1057402-11095-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>6113.73</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1057402-10618-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>5715.37</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/magallanes.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -701,7 +701,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057402-6483-CM26</t>
+          <t>1057402-6584-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -756,13 +756,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7110.27</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1057402-6485-CM26</t>
+          <t>1057402-6483-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8393.73</v>
+        <v>7110.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1057402-6488-CM26</t>
+          <t>1057402-6485-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3859.73</v>
+        <v>8393.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057402-6510-CM26</t>
+          <t>1057402-6488-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1057402-6514-CM26</t>
+          <t>1057402-6510-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4353.24</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057402-6564-CM26</t>
+          <t>1057402-6514-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3859.73</v>
+        <v>4353.24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057402-6695-CM26</t>
+          <t>1057402-6564-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4040.37</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1057402-6566-CM26</t>
+          <t>1057402-6695-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4353.24</v>
+        <v>4040.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1057402-6569-CM26</t>
+          <t>1057402-6566-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4439.84</v>
+        <v>4353.24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1057402-6571-CM26</t>
+          <t>1057402-6569-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3859.73</v>
+        <v>4439.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1057402-6577-CM26</t>
+          <t>1057402-6571-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1372,7 +1372,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1057402-6581-CM26</t>
+          <t>1057402-6577-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1433,7 +1433,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1057402-6584-CM26</t>
+          <t>1057402-6581-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1494,7 +1494,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1057402-7273-CM26</t>
+          <t>1057402-7271-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5691.39</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1057402-7271-CM26</t>
+          <t>1057402-7247-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3714.9</v>
+        <v>5836.56</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1057402-7247-CM26</t>
+          <t>1057402-7273-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5836.56</v>
+        <v>5691.39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1057402-7241-CM26</t>
+          <t>1057402-7245-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3714.9</v>
+        <v>4273.24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1057402-7245-CM26</t>
+          <t>1057402-7196-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1778,28 +1778,32 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4273.24</v>
+        <v>6414.13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1057402-7006-CM26</t>
+          <t>1057402-7241-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1854,13 +1858,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7252.55</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057402-7196-CM26</t>
+          <t>1057402-7006-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1900,32 +1904,28 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6414.13</v>
+        <v>7252.55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057402-7447-CM26</t>
+          <t>1057402-7511-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6323.65</v>
+        <v>4281.44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057402-7507-CM26</t>
+          <t>1057402-7447-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2041,13 +2041,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3722.02</v>
+        <v>6323.65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057402-7509-CM26</t>
+          <t>1057402-7507-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4197.93</v>
+        <v>3722.02</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057402-7511-CM26</t>
+          <t>1057402-7509-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4281.44</v>
+        <v>4197.93</v>
       </c>
     </row>
     <row r="29">
@@ -2230,7 +2230,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1057402-8011-CM26</t>
+          <t>1057402-8189-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2270,22 +2270,26 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3744.07</v>
+        <v>7146.38</v>
       </c>
     </row>
     <row r="31">
@@ -2352,7 +2356,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1057402-8189-CM26</t>
+          <t>1057402-8011-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2392,26 +2396,22 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7146.38</v>
+        <v>3744.07</v>
       </c>
     </row>
     <row r="33">
@@ -2604,7 +2604,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057402-8322-CM26</t>
+          <t>1057402-8336-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2644,32 +2644,28 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2800.66</v>
+        <v>4552.93</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1057402-8334-CM26</t>
+          <t>1057402-8508-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2724,13 +2720,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>5201.68</v>
+        <v>5946.43</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1057402-8336-CM26</t>
+          <t>1057402-8511-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2785,13 +2781,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4552.93</v>
+        <v>4188.09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1057402-8508-CM26</t>
+          <t>1057402-8592-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2846,13 +2842,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5946.43</v>
+        <v>3784.84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1057402-8511-CM26</t>
+          <t>1057402-8322-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2892,28 +2888,32 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4188.09</v>
+        <v>2800.66</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057402-8592-CM26</t>
+          <t>1057402-8334-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3784.84</v>
+        <v>5201.68</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1057402-9135-CM26</t>
+          <t>1057402-8807-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3029,13 +3029,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4463.31</v>
+        <v>3710.34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1057402-8811-CM26</t>
+          <t>1057402-8818-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3090,13 +3090,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4105.65</v>
+        <v>5892.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057402-8807-CM26</t>
+          <t>1057402-9135-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3710.34</v>
+        <v>4463.31</v>
       </c>
     </row>
     <row r="45">
@@ -3218,7 +3218,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057402-8818-CM26</t>
+          <t>1057402-8811-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5892.31</v>
+        <v>4105.65</v>
       </c>
     </row>
     <row r="47">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3596,65 +3596,126 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>1057402-10659-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>4280.73</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>1057402-10618-CM26</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>61.607.901-8</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Magallanes</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
         <is>
           <t>TRIMED CHILE SPA</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="n">
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
         <v>5715.37</v>
       </c>
     </row>
